--- a/dataset_t6_grouped/results2/G1/G1_T0374L_W0041F0002T0006Z000C1N7_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T0374L_W0041F0002T0006Z000C1N7_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>58.1785162041521</v>
+        <v>9.454008883174717</v>
       </c>
       <c r="D2" t="n">
-        <v>41.29108205040116</v>
+        <v>6.709800833190188</v>
       </c>
       <c r="E2" t="n">
-        <v>15.5864550063864</v>
+        <v>2.53279893853779</v>
       </c>
       <c r="F2" t="n">
-        <v>10.92073021078849</v>
+        <v>1.77461865925313</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>38.20452882220136</v>
+        <v>6.208235933607721</v>
       </c>
       <c r="D3" t="n">
-        <v>38.17284736442761</v>
+        <v>6.203087696719487</v>
       </c>
       <c r="E3" t="n">
-        <v>15.5864550063864</v>
+        <v>2.53279893853779</v>
       </c>
       <c r="F3" t="n">
-        <v>10.92073021078849</v>
+        <v>1.77461865925313</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>15.01782879395421</v>
+        <v>2.44039717901756</v>
       </c>
       <c r="D4" t="n">
-        <v>13.15902731967678</v>
+        <v>2.138341939447478</v>
       </c>
       <c r="E4" t="n">
-        <v>15.5864550063864</v>
+        <v>2.53279893853779</v>
       </c>
       <c r="F4" t="n">
-        <v>10.92073021078849</v>
+        <v>1.77461865925313</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>29.95889152963641</v>
+        <v>4.868319873565917</v>
       </c>
       <c r="D5" t="n">
-        <v>29.4885025245165</v>
+        <v>4.791881660233932</v>
       </c>
       <c r="E5" t="n">
-        <v>15.5864550063864</v>
+        <v>2.53279893853779</v>
       </c>
       <c r="F5" t="n">
-        <v>10.92073021078849</v>
+        <v>1.77461865925313</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
